--- a/FFMPYT-26 Scenario Builder.xlsx
+++ b/FFMPYT-26 Scenario Builder.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/k_el-shamaa_cgiar_org/Documents/ICARDA/Ongoing Activities/BCI/Designs/DiGGer/FFMPYT-26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kel-shamaa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="196" documentId="13_ncr:1_{A787EC9B-96CE-4496-A635-49C9DF07DAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB408FFA-D1E9-49AE-8956-CEDF4C3A5EE8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CFC1B0-A320-4232-8A14-D17C17F5EACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BD82420E-435A-4990-BD36-D6EF7A3E1476}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>Locations</t>
   </si>
@@ -153,13 +153,25 @@
   </si>
   <si>
     <t>dev.off()</t>
+  </si>
+  <si>
+    <t>Replication Ratio (%) per location</t>
+  </si>
+  <si>
+    <t>Connectivity Ratio (%) per location</t>
+  </si>
+  <si>
+    <t>fieldbook &lt;- fieldbook[order(fieldbook$Plot), c("Block", "Plot", "Row", "Col", "Entry")]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,6 +207,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -213,10 +232,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -238,9 +258,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -597,15 +621,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E82E0629-D810-4923-A763-8B7223C4C5FD}">
-  <dimension ref="A1:K308"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K311"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.44140625" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" customWidth="1"/>
-    <col min="5" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.42578125" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="5" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -613,7 +637,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -621,7 +645,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -629,7 +653,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -638,7 +662,7 @@
       </c>
       <c r="C4" s="7"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -646,7 +670,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -654,10 +678,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -666,7 +690,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -675,7 +699,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -684,7 +708,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -693,507 +717,527 @@
         <v>400</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="9">
+        <f>(B3 + B5) / (B3 + B5 + B9)</f>
+        <v>0.18343195266272189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="9">
+        <f>(B3 + B4) / (B3 + B5 + B9)</f>
+        <v>0.17455621301775148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B17" s="1">
         <v>20</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C17" s="1">
         <v>20</v>
       </c>
-      <c r="D14" s="1">
-        <f>$B$14*$C$14</f>
+      <c r="D17" s="1">
+        <f>$B$17*$C$17</f>
         <v>400</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B18" s="1">
         <v>20</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C18" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="1">
-        <f>$B$15*$C$15</f>
+      <c r="D18" s="1">
+        <f>$B$18*$C$18</f>
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" t="str">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="str">
         <f>"Block size = "&amp;B11/B6&amp;" ("&amp;B3&amp;" Checks entries + "&amp;B5&amp;" P-Rep Test entries + "&amp;B9/B6&amp;" Test entries)"</f>
         <v>Block size = 200 (8 Checks entries + 54 P-Rep Test entries + 138 Test entries)</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E19" s="8" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E22" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E23" s="1">
         <v>1</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F23" s="1">
         <v>2</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G23" s="1">
         <v>3</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H23" s="1">
         <v>4</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I23" s="1">
         <v>5</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J23" s="1">
         <v>6</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K23" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B24" s="1">
         <f>B6</f>
         <v>2</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C24" s="1">
         <f>B3</f>
         <v>8</v>
       </c>
-      <c r="D21" s="1">
-        <f>B21*C21</f>
+      <c r="D24" s="1">
+        <f>B24*C24</f>
         <v>16</v>
       </c>
-      <c r="E21" s="1" t="str">
+      <c r="E24" s="1" t="str">
         <f>$B$2+1&amp;" - "&amp;$B$2+$B$3</f>
         <v>2005 - 2012</v>
       </c>
-      <c r="F21" s="1" t="str">
-        <f t="shared" ref="F21:K21" si="0">$B$2+1&amp;" - "&amp;$B$2+$B$3</f>
+      <c r="F24" s="1" t="str">
+        <f t="shared" ref="F24:K24" si="0">$B$2+1&amp;" - "&amp;$B$2+$B$3</f>
         <v>2005 - 2012</v>
       </c>
-      <c r="G21" s="1" t="str">
+      <c r="G24" s="1" t="str">
         <f t="shared" si="0"/>
         <v>2005 - 2012</v>
       </c>
-      <c r="H21" s="1" t="str">
+      <c r="H24" s="1" t="str">
         <f t="shared" si="0"/>
         <v>2005 - 2012</v>
       </c>
-      <c r="I21" s="1" t="str">
+      <c r="I24" s="1" t="str">
         <f t="shared" si="0"/>
         <v>2005 - 2012</v>
       </c>
-      <c r="J21" s="1" t="str">
+      <c r="J24" s="1" t="str">
         <f t="shared" si="0"/>
         <v>2005 - 2012</v>
       </c>
-      <c r="K21" s="1" t="str">
+      <c r="K24" s="1" t="str">
         <f t="shared" si="0"/>
         <v>2005 - 2012</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B25" s="1">
         <v>1</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C25" s="1">
         <f>B4</f>
         <v>51</v>
       </c>
-      <c r="D22" s="1">
-        <f t="shared" ref="D22:D24" si="1">B22*C22</f>
+      <c r="D25" s="1">
+        <f t="shared" ref="D25:D27" si="1">B25*C25</f>
         <v>51</v>
       </c>
-      <c r="E22" s="1" t="str">
+      <c r="E25" s="1" t="str">
         <f>"1 - "&amp;$B$4</f>
         <v>1 - 51</v>
       </c>
-      <c r="F22" s="1" t="str">
-        <f t="shared" ref="F22:K22" si="2">"1 - "&amp;$B$4</f>
+      <c r="F25" s="1" t="str">
+        <f t="shared" ref="F25:K25" si="2">"1 - "&amp;$B$4</f>
         <v>1 - 51</v>
       </c>
-      <c r="G22" s="1" t="str">
+      <c r="G25" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1 - 51</v>
       </c>
-      <c r="H22" s="1" t="str">
+      <c r="H25" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1 - 51</v>
       </c>
-      <c r="I22" s="1" t="str">
+      <c r="I25" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1 - 51</v>
       </c>
-      <c r="J22" s="1" t="str">
+      <c r="J25" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1 - 51</v>
       </c>
-      <c r="K22" s="1" t="str">
+      <c r="K25" s="1" t="str">
         <f t="shared" si="2"/>
         <v>1 - 51</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B26" s="1">
         <f>B6</f>
         <v>2</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C26" s="1">
         <f>B5</f>
         <v>54</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D26" s="1">
         <f t="shared" si="1"/>
         <v>108</v>
       </c>
-      <c r="E23" s="1" t="str">
-        <f t="shared" ref="E23:G23" si="3">(E20-1)*$B$8+$B$4+1&amp;" - "&amp;(E20-1)*$B$8+$B$4+$B$5</f>
+      <c r="E26" s="1" t="str">
+        <f t="shared" ref="E26:G26" si="3">(E23-1)*$B$8+$B$4+1&amp;" - "&amp;(E23-1)*$B$8+$B$4+$B$5</f>
         <v>52 - 105</v>
       </c>
-      <c r="F23" s="1" t="str">
+      <c r="F26" s="1" t="str">
         <f t="shared" si="3"/>
         <v>331 - 384</v>
       </c>
-      <c r="G23" s="1" t="str">
+      <c r="G26" s="1" t="str">
         <f t="shared" si="3"/>
         <v>610 - 663</v>
       </c>
-      <c r="H23" s="1" t="str">
-        <f>(H20-1)*$B$8+$B$4+1&amp;" - "&amp;(H20-1)*$B$8+$B$4+$B$5</f>
+      <c r="H26" s="1" t="str">
+        <f>(H23-1)*$B$8+$B$4+1&amp;" - "&amp;(H23-1)*$B$8+$B$4+$B$5</f>
         <v>889 - 942</v>
       </c>
-      <c r="I23" s="1" t="str">
-        <f t="shared" ref="I23:K23" si="4">(I20-1)*$B$8+$B$4+1&amp;" - "&amp;(I20-1)*$B$8+$B$4+$B$5</f>
+      <c r="I26" s="1" t="str">
+        <f t="shared" ref="I26:K26" si="4">(I23-1)*$B$8+$B$4+1&amp;" - "&amp;(I23-1)*$B$8+$B$4+$B$5</f>
         <v>1168 - 1221</v>
       </c>
-      <c r="J23" s="1" t="str">
+      <c r="J26" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1447 - 1500</v>
       </c>
-      <c r="K23" s="1" t="str">
+      <c r="K26" s="1" t="str">
         <f t="shared" si="4"/>
         <v>1726 - 1779</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B27" s="1">
         <v>1</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C27" s="1">
         <f>B10</f>
         <v>225</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D27" s="1">
         <f t="shared" si="1"/>
         <v>225</v>
       </c>
-      <c r="E24" s="1" t="str">
-        <f>(E20-1)*$B$8+$B$4+$B$5+1&amp;" - "&amp;(E20-1)*$B$8+$B$5+$B$4+$B$10</f>
+      <c r="E27" s="1" t="str">
+        <f>(E23-1)*$B$8+$B$4+$B$5+1&amp;" - "&amp;(E23-1)*$B$8+$B$5+$B$4+$B$10</f>
         <v>106 - 330</v>
       </c>
-      <c r="F24" s="1" t="str">
-        <f>(F20-1)*$B$8+$B$4+$B$5+1&amp;" - "&amp;(F20-1)*$B$8+$B$5+$B$4+$B$10</f>
+      <c r="F27" s="1" t="str">
+        <f>(F23-1)*$B$8+$B$4+$B$5+1&amp;" - "&amp;(F23-1)*$B$8+$B$5+$B$4+$B$10</f>
         <v>385 - 609</v>
       </c>
-      <c r="G24" s="1" t="str">
-        <f>(G20-1)*$B$8+$B$4+$B$5+1&amp;" - "&amp;(G20-1)*$B$8+$B$5+$B$4+$B$10</f>
+      <c r="G27" s="1" t="str">
+        <f>(G23-1)*$B$8+$B$4+$B$5+1&amp;" - "&amp;(G23-1)*$B$8+$B$5+$B$4+$B$10</f>
         <v>664 - 888</v>
       </c>
-      <c r="H24" s="1" t="str">
-        <f>(H20-1)*$B$8+$B$4+$B$5+1&amp;" - "&amp;(H20-1)*$B$8+$B$5+$B$4+$B$10</f>
+      <c r="H27" s="1" t="str">
+        <f>(H23-1)*$B$8+$B$4+$B$5+1&amp;" - "&amp;(H23-1)*$B$8+$B$5+$B$4+$B$10</f>
         <v>943 - 1167</v>
       </c>
-      <c r="I24" s="1" t="str">
-        <f t="shared" ref="I24:K24" si="5">(I20-1)*$B$8+$B$4+$B$5+1&amp;" - "&amp;(I20-1)*$B$8+$B$5+$B$4+$B$10</f>
+      <c r="I27" s="1" t="str">
+        <f t="shared" ref="I27:K27" si="5">(I23-1)*$B$8+$B$4+$B$5+1&amp;" - "&amp;(I23-1)*$B$8+$B$5+$B$4+$B$10</f>
         <v>1222 - 1446</v>
       </c>
-      <c r="J24" s="1" t="str">
+      <c r="J27" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1501 - 1725</v>
       </c>
-      <c r="K24" s="1" t="str">
+      <c r="K27" s="1" t="str">
         <f t="shared" si="5"/>
         <v>1780 - 2004</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B29" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+    <row r="30" spans="1:11" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+      <c r="B30" s="1"/>
+    </row>
+    <row r="31" spans="1:11" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A29" s="4"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="str">
+    <row r="32" spans="1:11" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A32" s="4"/>
+    </row>
+    <row r="33" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="str">
         <f>"entries &lt;- "&amp;$B$8+$B$4+$B$3</f>
         <v>entries &lt;- 338</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="str">
-        <f>"field.rows &lt;- "&amp;B14</f>
+    <row r="34" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="str">
+        <f>"field.rows &lt;- "&amp;B17</f>
         <v>field.rows &lt;- 20</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="str">
-        <f>"field.cols &lt;- "&amp;C14</f>
+    <row r="35" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="str">
+        <f>"field.cols &lt;- "&amp;C17</f>
         <v>field.cols &lt;- 20</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="str">
-        <f>"block.rows &lt;- "&amp;B15</f>
+    <row r="36" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="str">
+        <f>"block.rows &lt;- "&amp;B18</f>
         <v>block.rows &lt;- 20</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="str">
-        <f>"block.cols &lt;- "&amp;C15</f>
+    <row r="37" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A37" s="5" t="str">
+        <f>"block.cols &lt;- "&amp;C18</f>
         <v>block.cols &lt;- 10</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="str">
+    <row r="38" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="str">
         <f>"trt.rep &lt;- rep(c(1, "&amp;$B$6&amp;", 1, "&amp;$B$6&amp;"), c("&amp;$B$4&amp;", "&amp;$B$5&amp;", "&amp;$B$10&amp;", "&amp;$B$3&amp;"))"</f>
         <v>trt.rep &lt;- rep(c(1, 2, 1, 2), c(51, 54, 225, 8))</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="str">
-        <f>"trt.name &lt;- c(1:"&amp;$B$4&amp;", "&amp;($B$26-1)*$B$8+$B$4+1&amp;":"&amp;($B$26-1)*$B$8+$B$4+$B$5&amp;", "&amp;($B$26-1)*$B$8+$B$4+$B$5+1&amp;":"&amp;($B$26-1)*$B$8+$B$5+$B$4+$B$10&amp;", "&amp;$B$2+1&amp;":"&amp;$B$2+$B$3&amp;")"</f>
+    <row r="39" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="str">
+        <f>"trt.name &lt;- c(1:"&amp;$B$4&amp;", "&amp;($B$29-1)*$B$8+$B$4+1&amp;":"&amp;($B$29-1)*$B$8+$B$4+$B$5&amp;", "&amp;($B$29-1)*$B$8+$B$4+$B$5+1&amp;":"&amp;($B$29-1)*$B$8+$B$5+$B$4+$B$10&amp;", "&amp;$B$2+1&amp;":"&amp;$B$2+$B$3&amp;")"</f>
         <v>trt.name &lt;- c(1:51, 1726:1779, 1780:2004, 2005:2012)</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="5"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
+    <row r="40" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="5"/>
+    </row>
+    <row r="41" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
+    <row r="42" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
+    <row r="43" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
+    <row r="44" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
+    <row r="45" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
+    <row r="46" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="5"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
+    <row r="47" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A47" s="5"/>
+    </row>
+    <row r="48" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
+    <row r="49" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A49" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="5" t="s">
+    <row r="50" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="5"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="5" t="str">
-        <f>"png('layout-loc"&amp;$B$26&amp;".png', width = 1600, height = 800, res = 96)"</f>
-        <v>png('layout-loc7.png', width = 1600, height = 800, res = 96)</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="str">
-        <f>"desPlot(layout, c(1:"&amp;$B$4&amp;"), col = 'deepskyblue', new = TRUE)"</f>
-        <v>desPlot(layout, c(1:51), col = 'deepskyblue', new = TRUE)</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="5" t="str">
-        <f>"desPlot(layout, c("&amp;($B$26-1)*$B$8+$B$4+1&amp;":"&amp;($B$26-1)*$B$8+$B$4+$B$5&amp;"), col = 'khaki', new = FALSE)"</f>
-        <v>desPlot(layout, c(1726:1779), col = 'khaki', new = FALSE)</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A51" s="5"/>
+    </row>
+    <row r="52" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="str">
-        <f>"desPlot(layout, c("&amp;($B$26-1)*$B$8+$B$4+$B$5+1&amp;":"&amp;($B$26-1)*$B$8+$B$5+$B$4+$B$10&amp;"), col = 'palegreen', new = FALSE)"</f>
-        <v>desPlot(layout, c(1780:2004), col = 'palegreen', new = FALSE)</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+        <f>"png('layout-loc"&amp;$B$29&amp;".png', width = 2400, height = 1200, res = 96)"</f>
+        <v>png('layout-loc7.png', width = 2400, height = 1200, res = 96)</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="str">
-        <f>"desPlot(layout, c("&amp;$B$2+1&amp;":"&amp;$B$2+$B$3&amp;"), col = 'violet', new = FALSE)"</f>
-        <v>desPlot(layout, c(2005:2012), col = 'violet', new = FALSE)</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="5" t="s">
+        <f>"desPlot(layout, c(1:"&amp;$B$4&amp;"), col = '#B9D9FF', new = TRUE)"</f>
+        <v>desPlot(layout, c(1:51), col = '#B9D9FF', new = TRUE)</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="str">
+        <f>"desPlot(layout, c("&amp;($B$29-1)*$B$8+$B$4+1&amp;":"&amp;($B$29-1)*$B$8+$B$4+$B$5&amp;"), col = '#F0E68C', new = FALSE)"</f>
+        <v>desPlot(layout, c(1726:1779), col = '#F0E68C', new = FALSE)</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A55" s="5" t="str">
+        <f>"desPlot(layout, c("&amp;($B$29-1)*$B$8+$B$4+$B$5+1&amp;":"&amp;($B$29-1)*$B$8+$B$5+$B$4+$B$10&amp;"), col = '#C9E7B7', new = FALSE)"</f>
+        <v>desPlot(layout, c(1780:2004), col = '#C9E7B7', new = FALSE)</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="str">
+        <f>"desPlot(layout, c("&amp;$B$2+1&amp;":"&amp;$B$2+$B$3&amp;"), col = '#F7B2B7', new = FALSE)"</f>
+        <v>desPlot(layout, c(2005:2012), col = '#F7B2B7', new = FALSE)</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="5" t="s">
+    <row r="58" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A58" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="5"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
+    <row r="59" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A59" s="5"/>
+    </row>
+    <row r="60" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="s">
+    <row r="61" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="5" t="str">
-        <f>"fieldbook$Block &lt;- rep(1:"&amp;$B$6&amp;", each="&amp;$D$15&amp;")"</f>
+    <row r="62" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A62" s="5" t="str">
+        <f>"fieldbook$Block &lt;- rep(1:"&amp;$B$6&amp;", each="&amp;$D$18&amp;")"</f>
         <v>fieldbook$Block &lt;- rep(1:2, each=200)</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="5"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="5" t="str">
-        <f>"fieldbook$Plot &lt;- with(fieldbook, "&amp;B15&amp;"*(Col-1) + Row + (1-Col%%2)*("&amp;B15+1&amp;"-2*Row))"</f>
+    <row r="63" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A63" s="5"/>
+    </row>
+    <row r="64" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A64" s="5" t="str">
+        <f>"fieldbook$Plot &lt;- with(fieldbook, "&amp;B18&amp;"*(Col-1) + Row + (1-Col%%2)*("&amp;B18+1&amp;"-2*Row))"</f>
         <v>fieldbook$Plot &lt;- with(fieldbook, 20*(Col-1) + Row + (1-Col%%2)*(21-2*Row))</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="5" t="str">
-        <f>"fieldbook &lt;- fieldbook[order(fieldbook$Plot),]"</f>
-        <v>fieldbook &lt;- fieldbook[order(fieldbook$Plot),]</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="5"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="5" t="str">
-        <f>"write.csv(fieldbook, 'fieldbook-loc"&amp;$B$26&amp;".csv', row.names = FALSE)"</f>
+    <row r="65" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A65" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A66" s="5"/>
+    </row>
+    <row r="67" spans="1:1" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A67" s="5" t="str">
+        <f>"write.csv(fieldbook, 'fieldbook-loc"&amp;$B$29&amp;".csv', row.names = FALSE)"</f>
         <v>write.csv(fieldbook, 'fieldbook-loc7.csv', row.names = FALSE)</v>
       </c>
     </row>
-    <row r="308" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C308" t="s">
+    <row r="311" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C311" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="E19:K19"/>
+    <mergeCell ref="E22:K22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B15">
+  <conditionalFormatting sqref="B18">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
-      <formula>$B$14</formula>
+      <formula>$B$17</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C15">
+  <conditionalFormatting sqref="C18">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
-      <formula>$C$14</formula>
+      <formula>$C$17</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D14">
+  <conditionalFormatting sqref="D17">
     <cfRule type="cellIs" dxfId="1" priority="4" operator="notEqual">
       <formula>$B$11</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D15">
+  <conditionalFormatting sqref="D18">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="notEqual">
       <formula>$B$11/$B$6</formula>
     </cfRule>
@@ -1204,21 +1248,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010001DED51D8AB1184E8865A1D6D2530336" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dc9cb3b101cf6c9591f1808175c6a0a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7638994b-6920-40e2-b996-68a0f82904f2" xmlns:ns4="cc44b21c-aa89-4bbd-ba66-f09e1816ba12" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="04a1eecd3e937892f97ea9974f2bc0d9" ns3:_="" ns4:_="">
     <xsd:import namespace="7638994b-6920-40e2-b996-68a0f82904f2"/>
@@ -1441,24 +1470,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{605208F4-F75E-486E-A1CC-7E5E57ECC579}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77CC7EB2-2A2F-42C6-8545-E2BE304634E0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22E3AE07-52C1-469E-8E3F-C860AC8EA6AF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1475,4 +1502,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77CC7EB2-2A2F-42C6-8545-E2BE304634E0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{605208F4-F75E-486E-A1CC-7E5E57ECC579}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>